--- a/AAII_Financials/Yearly/LAES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LAES_YR_FIN.xlsx
@@ -2344,10 +2344,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16400</v>
+        <v>10700</v>
       </c>
       <c r="E59" s="3">
-        <v>4300</v>
+        <v>2900</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
